--- a/diseases/d155/2010-2014.xlsx
+++ b/diseases/d155/2010-2014.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>35</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0.6525771530314866</v>
       </c>
@@ -1309,9 +1306,6 @@
       <c r="O5" t="n">
         <v>6</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0.1227204171185164</v>
       </c>
@@ -1853,9 +1847,6 @@
       <c r="O8" t="n">
         <v>20</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.3729012303037066</v>
       </c>
@@ -2249,9 +2240,6 @@
       <c r="O10" t="n">
         <v>3</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.06136020855925821</v>
       </c>
@@ -2793,9 +2781,6 @@
       <c r="O13" t="n">
         <v>63</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>1.174638875456676</v>
       </c>
@@ -3189,9 +3174,6 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
@@ -3733,9 +3715,6 @@
       <c r="O18" t="n">
         <v>42</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.7830925836377839</v>
       </c>
@@ -4129,9 +4108,6 @@
       <c r="O20" t="n">
         <v>5</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.1022670142654304</v>
       </c>
@@ -4673,9 +4649,6 @@
       <c r="O23" t="n">
         <v>68</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>1.267864183032603</v>
       </c>
@@ -5069,9 +5042,6 @@
       <c r="O25" t="n">
         <v>1</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0.02045340285308607</v>
       </c>
@@ -5613,9 +5583,6 @@
       <c r="O28" t="n">
         <v>57</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>1.062768506365564</v>
       </c>
@@ -6009,9 +5976,6 @@
       <c r="O30" t="n">
         <v>8</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.1636272228246886</v>
       </c>
@@ -6553,9 +6517,6 @@
       <c r="O33" t="n">
         <v>31</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0.5779969069707452</v>
       </c>
@@ -6949,9 +6910,6 @@
       <c r="O35" t="n">
         <v>5</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0.1022670142654304</v>
       </c>
@@ -7493,9 +7451,6 @@
       <c r="O38" t="n">
         <v>51</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.9508981372744518</v>
       </c>
@@ -7889,9 +7844,6 @@
       <c r="O40" t="n">
         <v>8</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.1636272228246886</v>
       </c>
@@ -8433,9 +8385,6 @@
       <c r="O43" t="n">
         <v>50</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0.9322530757592664</v>
       </c>
@@ -8829,9 +8778,6 @@
       <c r="O45" t="n">
         <v>5</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0.1022670142654304</v>
       </c>
@@ -9373,9 +9319,6 @@
       <c r="O48" t="n">
         <v>36</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0.6712222145466719</v>
       </c>
@@ -9769,9 +9712,6 @@
       <c r="O50" t="n">
         <v>4</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.08181361141234429</v>
       </c>
@@ -10313,9 +10253,6 @@
       <c r="O53" t="n">
         <v>41</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0.7644475221225986</v>
       </c>
@@ -10709,9 +10646,6 @@
       <c r="O55" t="n">
         <v>4</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0.08181361141234429</v>
       </c>
@@ -11253,9 +11187,6 @@
       <c r="O58" t="n">
         <v>33</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.615287030001116</v>
       </c>
@@ -11649,9 +11580,6 @@
       <c r="O60" t="n">
         <v>4</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.08181361141234429</v>
       </c>
@@ -12193,9 +12121,6 @@
       <c r="O63" t="n">
         <v>41</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0.760916224793954</v>
       </c>
@@ -12589,9 +12514,6 @@
       <c r="O65" t="n">
         <v>6</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.121139486465489</v>
       </c>
@@ -13133,9 +13055,6 @@
       <c r="O68" t="n">
         <v>47</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.8722698186662401</v>
       </c>
@@ -13529,9 +13448,6 @@
       <c r="O70" t="n">
         <v>3</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.06056974323274449</v>
       </c>
@@ -14073,9 +13989,6 @@
       <c r="O73" t="n">
         <v>54</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>1.002182344850574</v>
       </c>
@@ -14469,9 +14382,6 @@
       <c r="O75" t="n">
         <v>18</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0.3634184593964669</v>
       </c>
@@ -15013,9 +14923,6 @@
       <c r="O78" t="n">
         <v>39</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.7237983601698588</v>
       </c>
@@ -15409,9 +15316,6 @@
       <c r="O80" t="n">
         <v>6</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.121139486465489</v>
       </c>
@@ -15953,9 +15857,6 @@
       <c r="O83" t="n">
         <v>51</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0.9465055479144308</v>
       </c>
@@ -16349,9 +16250,6 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
@@ -16893,9 +16791,6 @@
       <c r="O88" t="n">
         <v>51</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0.9465055479144308</v>
       </c>
@@ -17289,9 +17184,6 @@
       <c r="O90" t="n">
         <v>5</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.1009495720545741</v>
       </c>
@@ -17833,9 +17725,6 @@
       <c r="O93" t="n">
         <v>39</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0.7237983601698588</v>
       </c>
@@ -18229,9 +18118,6 @@
       <c r="O95" t="n">
         <v>2</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0.04037982882182966</v>
       </c>
@@ -18773,9 +18659,6 @@
       <c r="O98" t="n">
         <v>82</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>1.521832449587908</v>
       </c>
@@ -19169,9 +19052,6 @@
       <c r="O100" t="n">
         <v>6</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.121139486465489</v>
       </c>
@@ -19713,9 +19593,6 @@
       <c r="O103" t="n">
         <v>44</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0.8165930217300971</v>
       </c>
@@ -20109,9 +19986,6 @@
       <c r="O105" t="n">
         <v>2</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0.04037982882182966</v>
       </c>
@@ -20653,9 +20527,6 @@
       <c r="O108" t="n">
         <v>25</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0.4639733078011915</v>
       </c>
@@ -21049,9 +20920,6 @@
       <c r="O110" t="n">
         <v>8</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.1615193152873186</v>
       </c>
@@ -21593,9 +21461,6 @@
       <c r="O113" t="n">
         <v>34</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0.6310036986096205</v>
       </c>
@@ -21989,9 +21854,6 @@
       <c r="O115" t="n">
         <v>3</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0.06056974323274449</v>
       </c>
@@ -22533,9 +22395,6 @@
       <c r="O118" t="n">
         <v>47</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.8722698186662401</v>
       </c>
@@ -22929,9 +22788,6 @@
       <c r="O120" t="n">
         <v>1</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0.02018991441091483</v>
       </c>
@@ -23473,9 +23329,6 @@
       <c r="O123" t="n">
         <v>39</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0.7203584281889922</v>
       </c>
@@ -23869,9 +23722,6 @@
       <c r="O125" t="n">
         <v>3</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0.05977932462315363</v>
       </c>
@@ -24413,9 +24263,6 @@
       <c r="O128" t="n">
         <v>27</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0.4987096810539177</v>
       </c>
@@ -24809,9 +24656,6 @@
       <c r="O130" t="n">
         <v>2</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.03985288308210241</v>
       </c>
@@ -25353,9 +25197,6 @@
       <c r="O133" t="n">
         <v>55</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>1.015890091035758</v>
       </c>
@@ -25749,9 +25590,6 @@
       <c r="O135" t="n">
         <v>2</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0.03985288308210241</v>
       </c>
@@ -26293,9 +26131,6 @@
       <c r="O138" t="n">
         <v>47</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0.868124259612375</v>
       </c>
@@ -26689,9 +26524,6 @@
       <c r="O140" t="n">
         <v>1</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0.01992644154105121</v>
       </c>
@@ -27233,9 +27065,6 @@
       <c r="O143" t="n">
         <v>61</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>1.126714464603295</v>
       </c>
@@ -27629,9 +27458,6 @@
       <c r="O145" t="n">
         <v>2</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0.03985288308210241</v>
       </c>
@@ -28173,9 +27999,6 @@
       <c r="O148" t="n">
         <v>71</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>1.311421753882524</v>
       </c>
@@ -28569,9 +28392,6 @@
       <c r="O150" t="n">
         <v>4</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0.07970576616420483</v>
       </c>
@@ -29113,9 +28933,6 @@
       <c r="O153" t="n">
         <v>50</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0.9235364463961437</v>
       </c>
@@ -29509,9 +29326,6 @@
       <c r="O155" t="n">
         <v>6</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0.1195586492463073</v>
       </c>
@@ -30053,9 +29867,6 @@
       <c r="O158" t="n">
         <v>70</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>1.292951024954601</v>
       </c>
@@ -30449,9 +30260,6 @@
       <c r="O160" t="n">
         <v>5</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0.09963220770525605</v>
       </c>
@@ -30993,9 +30801,6 @@
       <c r="O163" t="n">
         <v>28</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0.5171804099818404</v>
       </c>
@@ -31389,9 +31194,6 @@
       <c r="O165" t="n">
         <v>4</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0.07970576616420483</v>
       </c>
@@ -31933,9 +31735,6 @@
       <c r="O168" t="n">
         <v>42</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0.7757706149727607</v>
       </c>
@@ -32329,9 +32128,6 @@
       <c r="O170" t="n">
         <v>6</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0.1195586492463073</v>
       </c>
@@ -32873,9 +32669,6 @@
       <c r="O173" t="n">
         <v>41</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0.7572998860448379</v>
       </c>
@@ -33269,9 +33062,6 @@
       <c r="O175" t="n">
         <v>4</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>0.07970576616420483</v>
       </c>
@@ -33813,9 +33603,6 @@
       <c r="O178" t="n">
         <v>36</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0.6649462414052235</v>
       </c>
@@ -34209,9 +33996,6 @@
       <c r="O180" t="n">
         <v>4</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0.07970576616420483</v>
       </c>
@@ -34753,9 +34537,6 @@
       <c r="O183" t="n">
         <v>48</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>0.882506568698632</v>
       </c>
@@ -35149,9 +34930,6 @@
       <c r="O185" t="n">
         <v>4</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>0.07873822777374845</v>
       </c>
@@ -35693,9 +35471,6 @@
       <c r="O188" t="n">
         <v>37</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>0.6802654800385288</v>
       </c>
@@ -36089,9 +35864,6 @@
       <c r="O190" t="n">
         <v>3</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0.05905367083031134</v>
       </c>
@@ -36633,9 +36405,6 @@
       <c r="O193" t="n">
         <v>35</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0.6434943730094191</v>
       </c>
@@ -37029,9 +36798,6 @@
       <c r="O195" t="n">
         <v>4</v>
       </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
       <c r="R195" t="n">
         <v>0.07873822777374845</v>
       </c>
@@ -37573,9 +37339,6 @@
       <c r="O198" t="n">
         <v>70</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>1.286988746018838</v>
       </c>
@@ -37969,9 +37732,6 @@
       <c r="O200" t="n">
         <v>6</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0.1181073416606227</v>
       </c>
@@ -38513,9 +38273,6 @@
       <c r="O203" t="n">
         <v>39</v>
       </c>
-      <c r="Q203" t="n">
-        <v>0</v>
-      </c>
       <c r="R203" t="n">
         <v>0.7170365870676385</v>
       </c>
@@ -38909,9 +38666,6 @@
       <c r="O205" t="n">
         <v>7</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="R205" t="n">
         <v>0.1377918986040598</v>
       </c>
@@ -39453,9 +39207,6 @@
       <c r="O208" t="n">
         <v>50</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>0.9192776757277417</v>
       </c>
@@ -39849,9 +39600,6 @@
       <c r="O210" t="n">
         <v>6</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>0.1181073416606227</v>
       </c>
@@ -40393,9 +40141,6 @@
       <c r="O213" t="n">
         <v>42</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>0.7721932476113029</v>
       </c>
@@ -40789,9 +40534,6 @@
       <c r="O215" t="n">
         <v>1</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
       <c r="R215" t="n">
         <v>0.01968455694343711</v>
       </c>
@@ -41333,9 +41075,6 @@
       <c r="O218" t="n">
         <v>51</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0.9376632292422963</v>
       </c>
@@ -41729,9 +41468,6 @@
       <c r="O220" t="n">
         <v>4</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="R220" t="n">
         <v>0.07873822777374845</v>
       </c>
@@ -42273,9 +42009,6 @@
       <c r="O223" t="n">
         <v>41</v>
       </c>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
       <c r="R223" t="n">
         <v>0.7538076940967481</v>
       </c>
@@ -42669,9 +42402,6 @@
       <c r="O225" t="n">
         <v>4</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="R225" t="n">
         <v>0.07873822777374845</v>
       </c>
@@ -43213,9 +42943,6 @@
       <c r="O228" t="n">
         <v>33</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="R228" t="n">
         <v>0.6067232659803095</v>
       </c>
@@ -43609,9 +43336,6 @@
       <c r="O230" t="n">
         <v>8</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="R230" t="n">
         <v>0.1574764555474969</v>
       </c>
@@ -44153,9 +43877,6 @@
       <c r="O233" t="n">
         <v>46</v>
       </c>
-      <c r="Q233" t="n">
-        <v>0</v>
-      </c>
       <c r="R233" t="n">
         <v>0.8457354616695223</v>
       </c>
@@ -44549,9 +44270,6 @@
       <c r="O235" t="n">
         <v>4</v>
       </c>
-      <c r="Q235" t="n">
-        <v>0</v>
-      </c>
       <c r="R235" t="n">
         <v>0.07873822777374845</v>
       </c>
@@ -45093,9 +44811,6 @@
       <c r="O238" t="n">
         <v>57</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>1.047976550329625</v>
       </c>
@@ -45489,9 +45204,6 @@
       <c r="O240" t="n">
         <v>5</v>
       </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
       <c r="R240" t="n">
         <v>0.09842278471718557</v>
       </c>
@@ -46033,9 +45745,6 @@
       <c r="O243" t="n">
         <v>49</v>
       </c>
-      <c r="Q243" t="n">
-        <v>0</v>
-      </c>
       <c r="R243" t="n">
         <v>0.8971591911945106</v>
       </c>
@@ -46429,9 +46138,6 @@
       <c r="O245" t="n">
         <v>3</v>
       </c>
-      <c r="Q245" t="n">
-        <v>0</v>
-      </c>
       <c r="R245" t="n">
         <v>0.9159955726880653</v>
       </c>
@@ -46825,9 +46531,6 @@
       <c r="O247" t="n">
         <v>18</v>
       </c>
-      <c r="Q247" t="n">
-        <v>0</v>
-      </c>
       <c r="R247" t="n">
         <v>0.3503721243937832</v>
       </c>
@@ -47369,9 +47072,6 @@
       <c r="O250" t="n">
         <v>36</v>
       </c>
-      <c r="Q250" t="n">
-        <v>0</v>
-      </c>
       <c r="R250" t="n">
         <v>0.6591373649592324</v>
       </c>
@@ -47765,9 +47465,6 @@
       <c r="O252" t="n">
         <v>5</v>
       </c>
-      <c r="Q252" t="n">
-        <v>0</v>
-      </c>
       <c r="R252" t="n">
         <v>0.09732559010938423</v>
       </c>
@@ -48309,9 +48006,6 @@
       <c r="O255" t="n">
         <v>52</v>
       </c>
-      <c r="Q255" t="n">
-        <v>0</v>
-      </c>
       <c r="R255" t="n">
         <v>0.9520873049411134</v>
       </c>
@@ -48705,9 +48399,6 @@
       <c r="O257" t="n">
         <v>4</v>
       </c>
-      <c r="Q257" t="n">
-        <v>0</v>
-      </c>
       <c r="R257" t="n">
         <v>0.07786047208750739</v>
       </c>
@@ -49249,9 +48940,6 @@
       <c r="O260" t="n">
         <v>88</v>
       </c>
-      <c r="Q260" t="n">
-        <v>0</v>
-      </c>
       <c r="R260" t="n">
         <v>1.611224669900346</v>
       </c>
@@ -49645,9 +49333,6 @@
       <c r="O262" t="n">
         <v>14</v>
       </c>
-      <c r="Q262" t="n">
-        <v>0</v>
-      </c>
       <c r="R262" t="n">
         <v>0.2725116523062759</v>
       </c>
@@ -50189,9 +49874,6 @@
       <c r="O265" t="n">
         <v>31</v>
       </c>
-      <c r="Q265" t="n">
-        <v>0</v>
-      </c>
       <c r="R265" t="n">
         <v>0.5675905087148946</v>
       </c>
@@ -50585,9 +50267,6 @@
       <c r="O267" t="n">
         <v>121</v>
       </c>
-      <c r="Q267" t="n">
-        <v>0</v>
-      </c>
       <c r="R267" t="n">
         <v>2.355279280647098</v>
       </c>
@@ -51129,9 +50808,6 @@
       <c r="O270" t="n">
         <v>88</v>
       </c>
-      <c r="Q270" t="n">
-        <v>0</v>
-      </c>
       <c r="R270" t="n">
         <v>1.611224669900346</v>
       </c>
@@ -51525,9 +51201,6 @@
       <c r="O272" t="n">
         <v>7</v>
       </c>
-      <c r="Q272" t="n">
-        <v>0</v>
-      </c>
       <c r="R272" t="n">
         <v>0.1362558261531379</v>
       </c>
@@ -52069,9 +51742,6 @@
       <c r="O275" t="n">
         <v>53</v>
       </c>
-      <c r="Q275" t="n">
-        <v>0</v>
-      </c>
       <c r="R275" t="n">
         <v>0.9703966761899809</v>
       </c>
@@ -52465,9 +52135,6 @@
       <c r="O277" t="n">
         <v>7</v>
       </c>
-      <c r="Q277" t="n">
-        <v>0</v>
-      </c>
       <c r="R277" t="n">
         <v>0.1362558261531379</v>
       </c>
@@ -53009,9 +52676,6 @@
       <c r="O280" t="n">
         <v>43</v>
       </c>
-      <c r="Q280" t="n">
-        <v>0</v>
-      </c>
       <c r="R280" t="n">
         <v>0.7873029637013053</v>
       </c>
@@ -53405,9 +53069,6 @@
       <c r="O282" t="n">
         <v>12</v>
       </c>
-      <c r="Q282" t="n">
-        <v>0</v>
-      </c>
       <c r="R282" t="n">
         <v>0.2335814162625221</v>
       </c>
@@ -53949,9 +53610,6 @@
       <c r="O285" t="n">
         <v>39</v>
       </c>
-      <c r="Q285" t="n">
-        <v>0</v>
-      </c>
       <c r="R285" t="n">
         <v>0.7140654787058351</v>
       </c>
@@ -54345,9 +54003,6 @@
       <c r="O287" t="n">
         <v>5</v>
       </c>
-      <c r="Q287" t="n">
-        <v>0</v>
-      </c>
       <c r="R287" t="n">
         <v>0.09732559010938423</v>
       </c>
@@ -54889,9 +54544,6 @@
       <c r="O290" t="n">
         <v>30</v>
       </c>
-      <c r="Q290" t="n">
-        <v>0</v>
-      </c>
       <c r="R290" t="n">
         <v>0.549281137466027</v>
       </c>
@@ -55285,9 +54937,6 @@
       <c r="O292" t="n">
         <v>1</v>
       </c>
-      <c r="Q292" t="n">
-        <v>0</v>
-      </c>
       <c r="R292" t="n">
         <v>0.01946511802187685</v>
       </c>
@@ -55829,9 +55478,6 @@
       <c r="O295" t="n">
         <v>32</v>
       </c>
-      <c r="Q295" t="n">
-        <v>0</v>
-      </c>
       <c r="R295" t="n">
         <v>0.585899879963762</v>
       </c>
@@ -56225,9 +55871,6 @@
       <c r="O297" t="n">
         <v>13</v>
       </c>
-      <c r="Q297" t="n">
-        <v>0</v>
-      </c>
       <c r="R297" t="n">
         <v>0.253046534284399</v>
       </c>
@@ -56769,9 +56412,6 @@
       <c r="O300" t="n">
         <v>38</v>
       </c>
-      <c r="Q300" t="n">
-        <v>0</v>
-      </c>
       <c r="R300" t="n">
         <v>0.6957561074569675</v>
       </c>
@@ -57164,9 +56804,6 @@
       </c>
       <c r="O302" t="n">
         <v>4</v>
-      </c>
-      <c r="Q302" t="n">
-        <v>0</v>
       </c>
       <c r="R302" t="n">
         <v>0.07786047208750739</v>
